--- a/artfynd/A 48699-2025 artfynd.xlsx
+++ b/artfynd/A 48699-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66499921</v>
+        <v>66499923</v>
       </c>
       <c r="B2" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397790.5120825579</v>
+        <v>397762</v>
       </c>
       <c r="R2" t="n">
-        <v>6917589.477171307</v>
+        <v>6917586</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66499923</v>
+        <v>66499922</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397761.5821730195</v>
+        <v>397762</v>
       </c>
       <c r="R3" t="n">
-        <v>6917586.182811168</v>
+        <v>6917584</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,21 +845,11 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,12 +882,7 @@
         <v>66499926</v>
       </c>
       <c r="B4" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397749.1384284034</v>
+        <v>397749</v>
       </c>
       <c r="R4" t="n">
-        <v>6917528.987820061</v>
+        <v>6917529</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-08-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,12 +984,7 @@
         <v>66499927</v>
       </c>
       <c r="B5" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397702.3133414182</v>
+        <v>397702</v>
       </c>
       <c r="R5" t="n">
-        <v>6917518.347650304</v>
+        <v>6917518</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,19 +1049,9 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-08-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66499924</v>
+        <v>66499919</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397761.9687694046</v>
+        <v>397791</v>
       </c>
       <c r="R6" t="n">
-        <v>6917553.204494475</v>
+        <v>6917589</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1151,11 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66499925</v>
+        <v>66499924</v>
       </c>
       <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397761.9687694046</v>
+        <v>397762</v>
       </c>
       <c r="R7" t="n">
-        <v>6917553.204494475</v>
+        <v>6917553</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,21 +1253,11 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1359,7 +1269,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1377,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66499922</v>
+        <v>66499921</v>
       </c>
       <c r="B8" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397761.525436515</v>
+        <v>397791</v>
       </c>
       <c r="R8" t="n">
-        <v>6917584.327287227</v>
+        <v>6917589</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,21 +1355,11 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1476,7 +1371,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66499919</v>
+        <v>66499925</v>
       </c>
       <c r="B9" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>397790.5120825579</v>
+        <v>397762</v>
       </c>
       <c r="R9" t="n">
-        <v>6917589.477171307</v>
+        <v>6917553</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1567,21 +1457,11 @@
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2011-08-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1593,7 +1473,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 48699-2025 artfynd.xlsx
+++ b/artfynd/A 48699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499922</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499926</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499927</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499919</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499924</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499921</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,8 +1528,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66499925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>